--- a/uploads/2020/12/Time-Use-in-OECD-Countries-OECD.xlsx
+++ b/uploads/2020/12/Time-Use-in-OECD-Countries-OECD.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11108"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hannahr/Documents/OWID Topics/16 Culture, Values &amp; Society/Time Use/Time Use Patterns by Country (OECD)/Uploaded to WP/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Charlie/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B08AB582-FEE2-4F42-9280-656A990500A9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95556E12-FE3A-274D-AE8A-179CEF1E64CF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3580" yWindow="2560" windowWidth="27240" windowHeight="16440" xr2:uid="{AC39DB29-4830-4446-868B-914D3F2238E3}"/>
+    <workbookView xWindow="7480" yWindow="24780" windowWidth="27240" windowHeight="16440" xr2:uid="{AC39DB29-4830-4446-868B-914D3F2238E3}"/>
   </bookViews>
   <sheets>
     <sheet name="Time Use (OECD)" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,6 @@
     <externalReference r:id="rId2"/>
     <externalReference r:id="rId3"/>
     <externalReference r:id="rId4"/>
-    <externalReference r:id="rId5"/>
   </externalReferences>
   <definedNames>
     <definedName name="__123Graph_A" hidden="1">[1]A11!#REF!</definedName>
@@ -88,136 +87,136 @@
     <definedName name="__123Graph_XECTOT" hidden="1">#REF!</definedName>
     <definedName name="_1__123Graph_A_CURRENT" hidden="1">[1]A11!#REF!</definedName>
     <definedName name="_10__123Graph_A_CURRENT_8" hidden="1">[1]A11!#REF!</definedName>
-    <definedName name="_102__123Graph_D_CURRENT" hidden="1">[4]A11!#REF!</definedName>
-    <definedName name="_105__123Graph_D_CURRENT_1" hidden="1">[4]A11!#REF!</definedName>
-    <definedName name="_108__123Graph_D_CURRENT_10" hidden="1">[4]A11!#REF!</definedName>
+    <definedName name="_102__123Graph_D_CURRENT" hidden="1">[3]A11!#REF!</definedName>
+    <definedName name="_105__123Graph_D_CURRENT_1" hidden="1">[3]A11!#REF!</definedName>
+    <definedName name="_108__123Graph_D_CURRENT_10" hidden="1">[3]A11!#REF!</definedName>
     <definedName name="_11__123Graph_A_CURRENT_9" hidden="1">[1]A11!#REF!</definedName>
-    <definedName name="_111__123Graph_D_CURRENT_2" hidden="1">[4]A11!#REF!</definedName>
-    <definedName name="_114__123Graph_D_CURRENT_3" hidden="1">[4]A11!#REF!</definedName>
-    <definedName name="_117__123Graph_D_CURRENT_4" hidden="1">[4]A11!#REF!</definedName>
-    <definedName name="_12__123Graph_A_CURRENT_2" hidden="1">[4]A11!#REF!</definedName>
+    <definedName name="_111__123Graph_D_CURRENT_2" hidden="1">[3]A11!#REF!</definedName>
+    <definedName name="_114__123Graph_D_CURRENT_3" hidden="1">[3]A11!#REF!</definedName>
+    <definedName name="_117__123Graph_D_CURRENT_4" hidden="1">[3]A11!#REF!</definedName>
+    <definedName name="_12__123Graph_A_CURRENT_2" hidden="1">[3]A11!#REF!</definedName>
     <definedName name="_12__123Graph_B_CURRENT" hidden="1">[1]A11!#REF!</definedName>
-    <definedName name="_120__123Graph_D_CURRENT_5" hidden="1">[4]A11!#REF!</definedName>
-    <definedName name="_123__123Graph_D_CURRENT_6" hidden="1">[4]A11!#REF!</definedName>
-    <definedName name="_126__123Graph_D_CURRENT_7" hidden="1">[4]A11!#REF!</definedName>
-    <definedName name="_129__123Graph_D_CURRENT_8" hidden="1">[4]A11!#REF!</definedName>
+    <definedName name="_120__123Graph_D_CURRENT_5" hidden="1">[3]A11!#REF!</definedName>
+    <definedName name="_123__123Graph_D_CURRENT_6" hidden="1">[3]A11!#REF!</definedName>
+    <definedName name="_126__123Graph_D_CURRENT_7" hidden="1">[3]A11!#REF!</definedName>
+    <definedName name="_129__123Graph_D_CURRENT_8" hidden="1">[3]A11!#REF!</definedName>
     <definedName name="_13__123Graph_B_CURRENT_1" hidden="1">[1]A11!#REF!</definedName>
-    <definedName name="_132__123Graph_D_CURRENT_9" hidden="1">[4]A11!#REF!</definedName>
-    <definedName name="_135__123Graph_E_CURRENT" hidden="1">[4]A11!#REF!</definedName>
-    <definedName name="_138__123Graph_E_CURRENT_1" hidden="1">[4]A11!#REF!</definedName>
+    <definedName name="_132__123Graph_D_CURRENT_9" hidden="1">[3]A11!#REF!</definedName>
+    <definedName name="_135__123Graph_E_CURRENT" hidden="1">[3]A11!#REF!</definedName>
+    <definedName name="_138__123Graph_E_CURRENT_1" hidden="1">[3]A11!#REF!</definedName>
     <definedName name="_14__123Graph_B_CURRENT_10" hidden="1">[1]A11!#REF!</definedName>
-    <definedName name="_141__123Graph_E_CURRENT_10" hidden="1">[4]A11!#REF!</definedName>
-    <definedName name="_144__123Graph_E_CURRENT_2" hidden="1">[4]A11!#REF!</definedName>
-    <definedName name="_147__123Graph_E_CURRENT_3" hidden="1">[4]A11!#REF!</definedName>
-    <definedName name="_15__123Graph_A_CURRENT_3" hidden="1">[4]A11!#REF!</definedName>
+    <definedName name="_141__123Graph_E_CURRENT_10" hidden="1">[3]A11!#REF!</definedName>
+    <definedName name="_144__123Graph_E_CURRENT_2" hidden="1">[3]A11!#REF!</definedName>
+    <definedName name="_147__123Graph_E_CURRENT_3" hidden="1">[3]A11!#REF!</definedName>
+    <definedName name="_15__123Graph_A_CURRENT_3" hidden="1">[3]A11!#REF!</definedName>
     <definedName name="_15__123Graph_B_CURRENT_2" hidden="1">[1]A11!#REF!</definedName>
-    <definedName name="_150__123Graph_E_CURRENT_4" hidden="1">[4]A11!#REF!</definedName>
-    <definedName name="_153__123Graph_E_CURRENT_5" hidden="1">[4]A11!#REF!</definedName>
-    <definedName name="_156__123Graph_E_CURRENT_6" hidden="1">[4]A11!#REF!</definedName>
-    <definedName name="_159__123Graph_E_CURRENT_7" hidden="1">[4]A11!#REF!</definedName>
+    <definedName name="_150__123Graph_E_CURRENT_4" hidden="1">[3]A11!#REF!</definedName>
+    <definedName name="_153__123Graph_E_CURRENT_5" hidden="1">[3]A11!#REF!</definedName>
+    <definedName name="_156__123Graph_E_CURRENT_6" hidden="1">[3]A11!#REF!</definedName>
+    <definedName name="_159__123Graph_E_CURRENT_7" hidden="1">[3]A11!#REF!</definedName>
     <definedName name="_16__123Graph_B_CURRENT_3" hidden="1">[1]A11!#REF!</definedName>
-    <definedName name="_162__123Graph_E_CURRENT_8" hidden="1">[4]A11!#REF!</definedName>
-    <definedName name="_165__123Graph_E_CURRENT_9" hidden="1">[4]A11!#REF!</definedName>
-    <definedName name="_168__123Graph_F_CURRENT" hidden="1">[4]A11!#REF!</definedName>
+    <definedName name="_162__123Graph_E_CURRENT_8" hidden="1">[3]A11!#REF!</definedName>
+    <definedName name="_165__123Graph_E_CURRENT_9" hidden="1">[3]A11!#REF!</definedName>
+    <definedName name="_168__123Graph_F_CURRENT" hidden="1">[3]A11!#REF!</definedName>
     <definedName name="_17__123Graph_B_CURRENT_4" hidden="1">[1]A11!#REF!</definedName>
-    <definedName name="_171__123Graph_F_CURRENT_1" hidden="1">[4]A11!#REF!</definedName>
-    <definedName name="_174__123Graph_F_CURRENT_10" hidden="1">[4]A11!#REF!</definedName>
-    <definedName name="_177__123Graph_F_CURRENT_2" hidden="1">[4]A11!#REF!</definedName>
-    <definedName name="_18__123Graph_A_CURRENT_4" hidden="1">[4]A11!#REF!</definedName>
+    <definedName name="_171__123Graph_F_CURRENT_1" hidden="1">[3]A11!#REF!</definedName>
+    <definedName name="_174__123Graph_F_CURRENT_10" hidden="1">[3]A11!#REF!</definedName>
+    <definedName name="_177__123Graph_F_CURRENT_2" hidden="1">[3]A11!#REF!</definedName>
+    <definedName name="_18__123Graph_A_CURRENT_4" hidden="1">[3]A11!#REF!</definedName>
     <definedName name="_18__123Graph_B_CURRENT_5" hidden="1">[1]A11!#REF!</definedName>
-    <definedName name="_180__123Graph_F_CURRENT_3" hidden="1">[4]A11!#REF!</definedName>
-    <definedName name="_183__123Graph_F_CURRENT_4" hidden="1">[4]A11!#REF!</definedName>
-    <definedName name="_186__123Graph_F_CURRENT_5" hidden="1">[4]A11!#REF!</definedName>
-    <definedName name="_189__123Graph_F_CURRENT_6" hidden="1">[4]A11!#REF!</definedName>
+    <definedName name="_180__123Graph_F_CURRENT_3" hidden="1">[3]A11!#REF!</definedName>
+    <definedName name="_183__123Graph_F_CURRENT_4" hidden="1">[3]A11!#REF!</definedName>
+    <definedName name="_186__123Graph_F_CURRENT_5" hidden="1">[3]A11!#REF!</definedName>
+    <definedName name="_189__123Graph_F_CURRENT_6" hidden="1">[3]A11!#REF!</definedName>
     <definedName name="_19__123Graph_B_CURRENT_6" hidden="1">[1]A11!#REF!</definedName>
-    <definedName name="_192__123Graph_F_CURRENT_7" hidden="1">[4]A11!#REF!</definedName>
-    <definedName name="_195__123Graph_F_CURRENT_8" hidden="1">[4]A11!#REF!</definedName>
-    <definedName name="_198__123Graph_F_CURRENT_9" hidden="1">[4]A11!#REF!</definedName>
+    <definedName name="_192__123Graph_F_CURRENT_7" hidden="1">[3]A11!#REF!</definedName>
+    <definedName name="_195__123Graph_F_CURRENT_8" hidden="1">[3]A11!#REF!</definedName>
+    <definedName name="_198__123Graph_F_CURRENT_9" hidden="1">[3]A11!#REF!</definedName>
     <definedName name="_2__123Graph_A_CURRENT_1" hidden="1">[1]A11!#REF!</definedName>
     <definedName name="_20__123Graph_B_CURRENT_7" hidden="1">[1]A11!#REF!</definedName>
-    <definedName name="_21__123Graph_A_CURRENT_5" hidden="1">[4]A11!#REF!</definedName>
+    <definedName name="_21__123Graph_A_CURRENT_5" hidden="1">[3]A11!#REF!</definedName>
     <definedName name="_21__123Graph_B_CURRENT_8" hidden="1">[1]A11!#REF!</definedName>
     <definedName name="_22__123Graph_B_CURRENT_9" hidden="1">[1]A11!#REF!</definedName>
     <definedName name="_23__123Graph_C_CURRENT" hidden="1">[1]A11!#REF!</definedName>
-    <definedName name="_24__123Graph_A_CURRENT_6" hidden="1">[4]A11!#REF!</definedName>
+    <definedName name="_24__123Graph_A_CURRENT_6" hidden="1">[3]A11!#REF!</definedName>
     <definedName name="_24__123Graph_C_CURRENT_1" hidden="1">[1]A11!#REF!</definedName>
     <definedName name="_25__123Graph_C_CURRENT_10" hidden="1">[1]A11!#REF!</definedName>
     <definedName name="_26__123Graph_C_CURRENT_2" hidden="1">[1]A11!#REF!</definedName>
-    <definedName name="_27__123Graph_A_CURRENT_7" hidden="1">[4]A11!#REF!</definedName>
+    <definedName name="_27__123Graph_A_CURRENT_7" hidden="1">[3]A11!#REF!</definedName>
     <definedName name="_27__123Graph_C_CURRENT_3" hidden="1">[1]A11!#REF!</definedName>
     <definedName name="_28__123Graph_C_CURRENT_4" hidden="1">[1]A11!#REF!</definedName>
     <definedName name="_29__123Graph_C_CURRENT_5" hidden="1">[1]A11!#REF!</definedName>
-    <definedName name="_3__123Graph_A_CURRENT" hidden="1">[4]A11!#REF!</definedName>
+    <definedName name="_3__123Graph_A_CURRENT" hidden="1">[3]A11!#REF!</definedName>
     <definedName name="_3__123Graph_A_CURRENT_10" hidden="1">[1]A11!#REF!</definedName>
-    <definedName name="_30__123Graph_A_CURRENT_8" hidden="1">[4]A11!#REF!</definedName>
+    <definedName name="_30__123Graph_A_CURRENT_8" hidden="1">[3]A11!#REF!</definedName>
     <definedName name="_30__123Graph_C_CURRENT_6" hidden="1">[1]A11!#REF!</definedName>
     <definedName name="_31__123Graph_C_CURRENT_7" hidden="1">[1]A11!#REF!</definedName>
     <definedName name="_32__123Graph_C_CURRENT_8" hidden="1">[1]A11!#REF!</definedName>
-    <definedName name="_33__123Graph_A_CURRENT_9" hidden="1">[4]A11!#REF!</definedName>
+    <definedName name="_33__123Graph_A_CURRENT_9" hidden="1">[3]A11!#REF!</definedName>
     <definedName name="_33__123Graph_C_CURRENT_9" hidden="1">[1]A11!#REF!</definedName>
     <definedName name="_34__123Graph_D_CURRENT" hidden="1">[1]A11!#REF!</definedName>
     <definedName name="_35__123Graph_D_CURRENT_1" hidden="1">[1]A11!#REF!</definedName>
-    <definedName name="_36__123Graph_B_CURRENT" hidden="1">[4]A11!#REF!</definedName>
+    <definedName name="_36__123Graph_B_CURRENT" hidden="1">[3]A11!#REF!</definedName>
     <definedName name="_36__123Graph_D_CURRENT_10" hidden="1">[1]A11!#REF!</definedName>
     <definedName name="_37__123Graph_D_CURRENT_2" hidden="1">[1]A11!#REF!</definedName>
     <definedName name="_38__123Graph_D_CURRENT_3" hidden="1">[1]A11!#REF!</definedName>
-    <definedName name="_39__123Graph_B_CURRENT_1" hidden="1">[4]A11!#REF!</definedName>
+    <definedName name="_39__123Graph_B_CURRENT_1" hidden="1">[3]A11!#REF!</definedName>
     <definedName name="_39__123Graph_D_CURRENT_4" hidden="1">[1]A11!#REF!</definedName>
     <definedName name="_4__123Graph_A_CURRENT_2" hidden="1">[1]A11!#REF!</definedName>
     <definedName name="_40__123Graph_D_CURRENT_5" hidden="1">[1]A11!#REF!</definedName>
     <definedName name="_41__123Graph_D_CURRENT_6" hidden="1">[1]A11!#REF!</definedName>
-    <definedName name="_42__123Graph_B_CURRENT_10" hidden="1">[4]A11!#REF!</definedName>
+    <definedName name="_42__123Graph_B_CURRENT_10" hidden="1">[3]A11!#REF!</definedName>
     <definedName name="_42__123Graph_D_CURRENT_7" hidden="1">[1]A11!#REF!</definedName>
     <definedName name="_43__123Graph_D_CURRENT_8" hidden="1">[1]A11!#REF!</definedName>
     <definedName name="_44__123Graph_D_CURRENT_9" hidden="1">[1]A11!#REF!</definedName>
-    <definedName name="_45__123Graph_B_CURRENT_2" hidden="1">[4]A11!#REF!</definedName>
+    <definedName name="_45__123Graph_B_CURRENT_2" hidden="1">[3]A11!#REF!</definedName>
     <definedName name="_45__123Graph_E_CURRENT" hidden="1">[1]A11!#REF!</definedName>
     <definedName name="_46__123Graph_E_CURRENT_1" hidden="1">[1]A11!#REF!</definedName>
     <definedName name="_47__123Graph_E_CURRENT_10" hidden="1">[1]A11!#REF!</definedName>
-    <definedName name="_48__123Graph_B_CURRENT_3" hidden="1">[4]A11!#REF!</definedName>
+    <definedName name="_48__123Graph_B_CURRENT_3" hidden="1">[3]A11!#REF!</definedName>
     <definedName name="_48__123Graph_E_CURRENT_2" hidden="1">[1]A11!#REF!</definedName>
     <definedName name="_49__123Graph_E_CURRENT_3" hidden="1">[1]A11!#REF!</definedName>
     <definedName name="_5__123Graph_A_CURRENT_3" hidden="1">[1]A11!#REF!</definedName>
     <definedName name="_50__123Graph_E_CURRENT_4" hidden="1">[1]A11!#REF!</definedName>
-    <definedName name="_51__123Graph_B_CURRENT_4" hidden="1">[4]A11!#REF!</definedName>
+    <definedName name="_51__123Graph_B_CURRENT_4" hidden="1">[3]A11!#REF!</definedName>
     <definedName name="_51__123Graph_E_CURRENT_5" hidden="1">[1]A11!#REF!</definedName>
     <definedName name="_52__123Graph_E_CURRENT_6" hidden="1">[1]A11!#REF!</definedName>
     <definedName name="_53__123Graph_E_CURRENT_7" hidden="1">[1]A11!#REF!</definedName>
-    <definedName name="_54__123Graph_B_CURRENT_5" hidden="1">[4]A11!#REF!</definedName>
+    <definedName name="_54__123Graph_B_CURRENT_5" hidden="1">[3]A11!#REF!</definedName>
     <definedName name="_54__123Graph_E_CURRENT_8" hidden="1">[1]A11!#REF!</definedName>
     <definedName name="_55__123Graph_E_CURRENT_9" hidden="1">[1]A11!#REF!</definedName>
     <definedName name="_56__123Graph_F_CURRENT" hidden="1">[1]A11!#REF!</definedName>
-    <definedName name="_57__123Graph_B_CURRENT_6" hidden="1">[4]A11!#REF!</definedName>
+    <definedName name="_57__123Graph_B_CURRENT_6" hidden="1">[3]A11!#REF!</definedName>
     <definedName name="_57__123Graph_F_CURRENT_1" hidden="1">[1]A11!#REF!</definedName>
     <definedName name="_58__123Graph_F_CURRENT_10" hidden="1">[1]A11!#REF!</definedName>
     <definedName name="_59__123Graph_F_CURRENT_2" hidden="1">[1]A11!#REF!</definedName>
-    <definedName name="_6__123Graph_A_CURRENT_1" hidden="1">[4]A11!#REF!</definedName>
+    <definedName name="_6__123Graph_A_CURRENT_1" hidden="1">[3]A11!#REF!</definedName>
     <definedName name="_6__123Graph_A_CURRENT_4" hidden="1">[1]A11!#REF!</definedName>
-    <definedName name="_60__123Graph_B_CURRENT_7" hidden="1">[4]A11!#REF!</definedName>
+    <definedName name="_60__123Graph_B_CURRENT_7" hidden="1">[3]A11!#REF!</definedName>
     <definedName name="_60__123Graph_F_CURRENT_3" hidden="1">[1]A11!#REF!</definedName>
     <definedName name="_61__123Graph_F_CURRENT_4" hidden="1">[1]A11!#REF!</definedName>
     <definedName name="_62__123Graph_F_CURRENT_5" hidden="1">[1]A11!#REF!</definedName>
-    <definedName name="_63__123Graph_B_CURRENT_8" hidden="1">[4]A11!#REF!</definedName>
+    <definedName name="_63__123Graph_B_CURRENT_8" hidden="1">[3]A11!#REF!</definedName>
     <definedName name="_63__123Graph_F_CURRENT_6" hidden="1">[1]A11!#REF!</definedName>
     <definedName name="_64__123Graph_F_CURRENT_7" hidden="1">[1]A11!#REF!</definedName>
     <definedName name="_65__123Graph_F_CURRENT_8" hidden="1">[1]A11!#REF!</definedName>
-    <definedName name="_66__123Graph_B_CURRENT_9" hidden="1">[4]A11!#REF!</definedName>
+    <definedName name="_66__123Graph_B_CURRENT_9" hidden="1">[3]A11!#REF!</definedName>
     <definedName name="_66__123Graph_F_CURRENT_9" hidden="1">[1]A11!#REF!</definedName>
-    <definedName name="_69__123Graph_C_CURRENT" hidden="1">[4]A11!#REF!</definedName>
+    <definedName name="_69__123Graph_C_CURRENT" hidden="1">[3]A11!#REF!</definedName>
     <definedName name="_7__123Graph_A_CURRENT_5" hidden="1">[1]A11!#REF!</definedName>
-    <definedName name="_72__123Graph_C_CURRENT_1" hidden="1">[4]A11!#REF!</definedName>
-    <definedName name="_75__123Graph_C_CURRENT_10" hidden="1">[4]A11!#REF!</definedName>
-    <definedName name="_78__123Graph_C_CURRENT_2" hidden="1">[4]A11!#REF!</definedName>
+    <definedName name="_72__123Graph_C_CURRENT_1" hidden="1">[3]A11!#REF!</definedName>
+    <definedName name="_75__123Graph_C_CURRENT_10" hidden="1">[3]A11!#REF!</definedName>
+    <definedName name="_78__123Graph_C_CURRENT_2" hidden="1">[3]A11!#REF!</definedName>
     <definedName name="_8__123Graph_A_CURRENT_6" hidden="1">[1]A11!#REF!</definedName>
-    <definedName name="_81__123Graph_C_CURRENT_3" hidden="1">[4]A11!#REF!</definedName>
-    <definedName name="_84__123Graph_C_CURRENT_4" hidden="1">[4]A11!#REF!</definedName>
-    <definedName name="_87__123Graph_C_CURRENT_5" hidden="1">[4]A11!#REF!</definedName>
-    <definedName name="_9__123Graph_A_CURRENT_10" hidden="1">[4]A11!#REF!</definedName>
+    <definedName name="_81__123Graph_C_CURRENT_3" hidden="1">[3]A11!#REF!</definedName>
+    <definedName name="_84__123Graph_C_CURRENT_4" hidden="1">[3]A11!#REF!</definedName>
+    <definedName name="_87__123Graph_C_CURRENT_5" hidden="1">[3]A11!#REF!</definedName>
+    <definedName name="_9__123Graph_A_CURRENT_10" hidden="1">[3]A11!#REF!</definedName>
     <definedName name="_9__123Graph_A_CURRENT_7" hidden="1">[1]A11!#REF!</definedName>
-    <definedName name="_90__123Graph_C_CURRENT_6" hidden="1">[4]A11!#REF!</definedName>
-    <definedName name="_93__123Graph_C_CURRENT_7" hidden="1">[4]A11!#REF!</definedName>
-    <definedName name="_96__123Graph_C_CURRENT_8" hidden="1">[4]A11!#REF!</definedName>
-    <definedName name="_99__123Graph_C_CURRENT_9" hidden="1">[4]A11!#REF!</definedName>
+    <definedName name="_90__123Graph_C_CURRENT_6" hidden="1">[3]A11!#REF!</definedName>
+    <definedName name="_93__123Graph_C_CURRENT_7" hidden="1">[3]A11!#REF!</definedName>
+    <definedName name="_96__123Graph_C_CURRENT_8" hidden="1">[3]A11!#REF!</definedName>
+    <definedName name="_99__123Graph_C_CURRENT_9" hidden="1">[3]A11!#REF!</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Time Use (OECD)'!$A$1:$C$459</definedName>
     <definedName name="_Order1" hidden="1">255</definedName>
     <definedName name="_Order2" hidden="1">255</definedName>
@@ -244,7 +243,7 @@
     <definedName name="HTML_PathFile" hidden="1">"I:\WORKING\EDSTATS\table43.htm"</definedName>
     <definedName name="HTML_Title" hidden="1">"table43"</definedName>
     <definedName name="tabx" hidden="1">{"g95_96m1",#N/A,FALSE,"Graf(95+96)M";"g95_96m2",#N/A,FALSE,"Graf(95+96)M";"g95_96mb1",#N/A,FALSE,"Graf(95+96)Mb";"g95_96mb2",#N/A,FALSE,"Graf(95+96)Mb";"g95_96f1",#N/A,FALSE,"Graf(95+96)F";"g95_96f2",#N/A,FALSE,"Graf(95+96)F";"g95_96fb1",#N/A,FALSE,"Graf(95+96)Fb";"g95_96fb2",#N/A,FALSE,"Graf(95+96)Fb"}</definedName>
-    <definedName name="temp" hidden="1">[4]A11!#REF!</definedName>
+    <definedName name="temp" hidden="1">[3]A11!#REF!</definedName>
     <definedName name="wrn.Graf95_96." hidden="1">{"g95_96m1",#N/A,FALSE,"Graf(95+96)M";"g95_96m2",#N/A,FALSE,"Graf(95+96)M";"g95_96mb1",#N/A,FALSE,"Graf(95+96)Mb";"g95_96mb2",#N/A,FALSE,"Graf(95+96)Mb";"g95_96f1",#N/A,FALSE,"Graf(95+96)F";"g95_96f2",#N/A,FALSE,"Graf(95+96)F";"g95_96fb1",#N/A,FALSE,"Graf(95+96)Fb";"g95_96fb2",#N/A,FALSE,"Graf(95+96)Fb"}</definedName>
     <definedName name="wrn.R22_Data_Collection1997." hidden="1">{"_R22_General",#N/A,TRUE,"R22_General";"_R22_Questions",#N/A,TRUE,"R22_Questions";"ColA_R22",#N/A,TRUE,"R2295";"_R22_Tables",#N/A,TRUE,"R2295"}</definedName>
     <definedName name="wrn.TabARA." hidden="1">{"Page1",#N/A,FALSE,"ARA M&amp;F&amp;T";"Page2",#N/A,FALSE,"ARA M&amp;F&amp;T";"Page3",#N/A,FALSE,"ARA M&amp;F&amp;T"}</definedName>
@@ -274,9 +273,6 @@
   </si>
   <si>
     <t>Category</t>
-  </si>
-  <si>
-    <t>Time (hours)</t>
   </si>
   <si>
     <t>Australia</t>
@@ -419,6 +415,9 @@
   <si>
     <t>Other leisure activities</t>
   </si>
+  <si>
+    <t>Time (minutes)</t>
+  </si>
 </sst>
 </file>
 
@@ -499,39 +498,6 @@
 </file>
 
 <file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Tableau chart"/>
-      <sheetName val="For Tableau"/>
-      <sheetName val="High-level chart"/>
-      <sheetName val="Sub-categories chart"/>
-      <sheetName val="Transposed"/>
-      <sheetName val="Total"/>
-      <sheetName val="Men"/>
-      <sheetName val="Women"/>
-      <sheetName val="Activity categories &amp; sources"/>
-      <sheetName val="Archive 2018"/>
-      <sheetName val="Read me"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -852,15 +818,15 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
         <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
       </c>
       <c r="C2" s="1">
         <v>211.1466296038916</v>
@@ -868,10 +834,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C3" s="1">
         <v>279.53226810278045</v>
@@ -879,10 +845,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C4" s="1">
         <v>194.47645218876283</v>
@@ -890,10 +856,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C5" s="1">
         <v>268.66060964789853</v>
@@ -901,10 +867,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C6" s="1">
         <v>199.77159591556563</v>
@@ -912,10 +878,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C7" s="1">
         <v>230.78802152293935</v>
@@ -923,10 +889,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C8" s="1">
         <v>200.04787899999999</v>
@@ -934,10 +900,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C9" s="1">
         <v>170.06064246744319</v>
@@ -945,10 +911,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" s="1">
         <v>223.83901233333333</v>
@@ -956,10 +922,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11" s="1">
         <v>187.36806030314426</v>
@@ -967,10 +933,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C12" s="1">
         <v>199.44677218041056</v>
@@ -978,10 +944,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C13" s="1">
         <v>231.22452000000001</v>
@@ -989,10 +955,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C14" s="1">
         <v>148.8945516673694</v>
@@ -1000,10 +966,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" s="1">
         <v>325.7113724006864</v>
@@ -1011,10 +977,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C16" s="1">
         <v>287.59684592368671</v>
@@ -1022,10 +988,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C17" s="1">
         <v>316.55785239539017</v>
@@ -1033,10 +999,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A18" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C18" s="1">
         <v>303.64728698359079</v>
@@ -1044,10 +1010,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A19" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C19" s="1">
         <v>247.22546126537438</v>
@@ -1055,10 +1021,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C20" s="1">
         <v>302.33356400000002</v>
@@ -1066,10 +1032,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A21" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C21" s="1">
         <v>217.63035631810573</v>
@@ -1077,10 +1043,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A22" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C22" s="1">
         <v>240.99999999999997</v>
@@ -1088,10 +1054,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C23" s="1">
         <v>200.78621999999999</v>
@@ -1099,10 +1065,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C24" s="1">
         <v>229.27929947160737</v>
@@ -1110,10 +1076,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A25" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C25" s="1">
         <v>258.79720279720283</v>
@@ -1121,10 +1087,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A26" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C26" s="1">
         <v>226.68515950069346</v>
@@ -1132,10 +1098,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A27" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C27" s="1">
         <v>175.7783</v>
@@ -1143,10 +1109,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A28" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C28" s="1">
         <v>262.18713699086243</v>
@@ -1154,10 +1120,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A29" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C29" s="1">
         <v>217.02784000000003</v>
@@ -1165,10 +1131,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A30" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C30" s="1">
         <v>235.49323385367586</v>
@@ -1176,10 +1142,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A31" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C31" s="1">
         <v>251.13777399999998</v>
@@ -1187,10 +1153,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A32" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C32" s="1">
         <v>314.78140180430256</v>
@@ -1198,10 +1164,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A33" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C33" s="1">
         <v>271.54098281283314</v>
@@ -1209,10 +1175,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A34" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C34" s="1">
         <v>188.80248</v>
@@ -1220,10 +1186,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A35" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B35" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C35" s="1">
         <v>27.01876302988186</v>
@@ -1231,10 +1197,10 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A36" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B36" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C36" s="1">
         <v>26.897949499999999</v>
@@ -1242,10 +1208,10 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A37" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B37" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C37" s="1">
         <v>41.27717150712752</v>
@@ -1253,10 +1219,10 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A38" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B38" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C38" s="1">
         <v>35.980636822399518</v>
@@ -1264,10 +1230,10 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A39" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B39" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C39" s="1">
         <v>25.044997704372655</v>
@@ -1275,10 +1241,10 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A40" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B40" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C40" s="1">
         <v>24.789344710195497</v>
@@ -1286,10 +1252,10 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A41" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B41" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C41" s="1">
         <v>29.049119999999998</v>
@@ -1297,10 +1263,10 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A42" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B42" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C42" s="1">
         <v>34.104501998902755</v>
@@ -1308,10 +1274,10 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A43" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B43" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C43" s="1">
         <v>24.042136666666668</v>
@@ -1319,10 +1285,10 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A44" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B44" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C44" s="1">
         <v>40.341823605539602</v>
@@ -1330,10 +1296,10 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A45" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B45" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C45" s="1">
         <v>38.167231251211099</v>
@@ -1341,10 +1307,10 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A46" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B46" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C46" s="1">
         <v>36.73677</v>
@@ -1352,10 +1318,10 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A47" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B47" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C47" s="1">
         <v>27.814506494490416</v>
@@ -1363,10 +1329,10 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A48" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B48" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C48" s="1">
         <v>36.979999999999997</v>
@@ -1374,10 +1340,10 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A49" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B49" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C49" s="1">
         <v>56.85552126968021</v>
@@ -1385,10 +1351,10 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A50" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B50" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C50" s="1">
         <v>13.380574479276921</v>
@@ -1396,10 +1362,10 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A51" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B51" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C51" s="1">
         <v>11.567863177310837</v>
@@ -1407,10 +1373,10 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A52" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B52" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C52" s="1">
         <v>37.462673231363127</v>
@@ -1418,10 +1384,10 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A53" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B53" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C53" s="1">
         <v>45.29898</v>
@@ -1429,10 +1395,10 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A54" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B54" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C54" s="1">
         <v>25.156676458305824</v>
@@ -1440,10 +1406,10 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A55" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B55" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C55" s="1">
         <v>29</v>
@@ -1451,10 +1417,10 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A56" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B56" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C56" s="1">
         <v>40.478844000000002</v>
@@ -1462,10 +1428,10 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A57" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B57" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C57" s="1">
         <v>30.307877310279011</v>
@@ -1473,10 +1439,10 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A58" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B58" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C58" s="1">
         <v>36.251748251748253</v>
@@ -1484,10 +1450,10 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A59" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B59" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C59" s="1">
         <v>37.947295423023576</v>
@@ -1495,10 +1461,10 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A60" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B60" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C60" s="1">
         <v>26.236302999999999</v>
@@ -1506,10 +1472,10 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A61" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B61" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C61" s="1">
         <v>31.219734784113403</v>
@@ -1517,10 +1483,10 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A62" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B62" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C62" s="1">
         <v>29.041440000000001</v>
@@ -1528,10 +1494,10 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A63" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B63" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C63" s="1">
         <v>26.771676014251472</v>
@@ -1539,10 +1505,10 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A64" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B64" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C64" s="1">
         <v>31.418909999999997</v>
@@ -1550,10 +1516,10 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A65" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B65" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C65" s="1">
         <v>24.98265093684941</v>
@@ -1561,10 +1527,10 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A66" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B66" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C66" s="1">
         <v>23.438432693168188</v>
@@ -1572,10 +1538,10 @@
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A67" t="s">
+        <v>35</v>
+      </c>
+      <c r="B67" t="s">
         <v>36</v>
-      </c>
-      <c r="B67" t="s">
-        <v>37</v>
       </c>
       <c r="C67" s="1">
         <v>38.810659999999999</v>
@@ -1583,10 +1549,10 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A68" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B68" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C68" s="1">
         <v>44.53092425295344</v>
@@ -1594,10 +1560,10 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A69" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B69" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C69" s="1">
         <v>33.88775526253324</v>
@@ -1605,10 +1571,10 @@
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A70" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B70" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C70" s="1">
         <v>22</v>
@@ -1616,10 +1582,10 @@
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A71" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B71" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C71" s="1">
         <v>29</v>
@@ -1627,10 +1593,10 @@
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A72" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B72" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C72" s="1">
         <v>28.495650686690823</v>
@@ -1638,10 +1604,10 @@
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A73" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B73" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C73" s="1">
         <v>27.928427598072435</v>
@@ -1649,10 +1615,10 @@
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A74" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B74" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C74" s="1">
         <v>22.939862899999998</v>
@@ -1660,10 +1626,10 @@
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A75" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B75" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C75" s="1">
         <v>22.116559396276116</v>
@@ -1671,10 +1637,10 @@
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A76" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B76" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C76" s="1">
         <v>18.901665333333334</v>
@@ -1682,10 +1648,10 @@
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A77" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B77" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C77" s="1">
         <v>19</v>
@@ -1693,10 +1659,10 @@
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A78" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B78" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C78" s="1">
         <v>33</v>
@@ -1704,10 +1670,10 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A79" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B79" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C79" s="1">
         <v>60.755940000000002</v>
@@ -1715,10 +1681,10 @@
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A80" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B80" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C80" s="1">
         <v>26.621509337390592</v>
@@ -1726,10 +1692,10 @@
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A81" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B81" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C81" s="1">
         <v>0</v>
@@ -1737,10 +1703,10 @@
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A82" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B82" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C82" s="1">
         <v>27.695620733488894</v>
@@ -1748,10 +1714,10 @@
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A83" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B83" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C83" s="1">
         <v>15</v>
@@ -1759,10 +1725,10 @@
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A84" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B84" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C84" s="1">
         <v>19</v>
@@ -1770,10 +1736,10 @@
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A85" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B85" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C85" s="1">
         <v>20</v>
@@ -1781,10 +1747,10 @@
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A86" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B86" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C86" s="1">
         <v>38.211546999999996</v>
@@ -1792,10 +1758,10 @@
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A87" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B87" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C87" s="1">
         <v>21.573036181474887</v>
@@ -1803,10 +1769,10 @@
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A88" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B88" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C88" s="1">
         <v>30</v>
@@ -1814,10 +1780,10 @@
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A89" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B89" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C89" s="1">
         <v>23</v>
@@ -1825,10 +1791,10 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A90" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B90" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C90" s="1">
         <v>38</v>
@@ -1836,10 +1802,10 @@
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A91" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B91" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C91" s="1">
         <v>17.118881118881117</v>
@@ -1847,10 +1813,10 @@
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A92" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B92" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C92" s="1">
         <v>20.970873786407768</v>
@@ -1858,10 +1824,10 @@
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A93" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B93" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C93" s="1">
         <v>35</v>
@@ -1869,10 +1835,10 @@
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A94" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B94" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C94" s="1">
         <v>32.536489508994187</v>
@@ -1880,10 +1846,10 @@
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A95" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B95" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C95" s="1">
         <v>28.504801</v>
@@ -1891,10 +1857,10 @@
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A96" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B96" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C96" s="1">
         <v>32.05350676738788</v>
@@ -1902,10 +1868,10 @@
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A97" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B97" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C97" s="1">
         <v>30.618279999999999</v>
@@ -1913,10 +1879,10 @@
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A98" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B98" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C98" s="1">
         <v>22.984038861901457</v>
@@ -1924,10 +1890,10 @@
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A99" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B99" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C99" s="1">
         <v>21.451138074992837</v>
@@ -1935,10 +1901,10 @@
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A100" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B100" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C100" s="1">
         <v>17.751244999999997</v>
@@ -1946,10 +1912,10 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A101" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B101" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C101" s="1">
         <v>132.09173036831132</v>
@@ -1957,10 +1923,10 @@
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A102" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B102" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C102" s="1">
         <v>124.59176206525849</v>
@@ -1968,10 +1934,10 @@
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A103" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B103" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C103" s="1">
         <v>120.53960311565456</v>
@@ -1979,10 +1945,10 @@
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A104" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B104" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C104" s="1">
         <v>114.68344777840595</v>
@@ -1990,10 +1956,10 @@
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A105" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B105" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C105" s="1">
         <v>127.55955140937537</v>
@@ -2001,10 +1967,10 @@
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A106" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B106" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C106" s="1">
         <v>120.66609002002623</v>
@@ -2012,10 +1978,10 @@
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A107" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B107" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C107" s="1">
         <v>109.4122</v>
@@ -2023,10 +1989,10 @@
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A108" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B108" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C108" s="1">
         <v>128.50020753153993</v>
@@ -2034,10 +2000,10 @@
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A109" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B109" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C109" s="1">
         <v>109.35420000000001</v>
@@ -2045,10 +2011,10 @@
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A110" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B110" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C110" s="1">
         <v>124.52283553974084</v>
@@ -2056,10 +2022,10 @@
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A111" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B111" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C111" s="1">
         <v>149.95613874609404</v>
@@ -2067,10 +2033,10 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A112" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B112" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C112" s="1">
         <v>90.748580000000004</v>
@@ -2078,10 +2044,10 @@
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A113" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B113" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C113" s="1">
         <v>134.71427265092865</v>
@@ -2089,10 +2055,10 @@
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A114" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B114" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C114" s="1">
         <v>80.370472535380202</v>
@@ -2100,10 +2066,10 @@
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A115" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B115" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C115" s="1">
         <v>76.162790481758975</v>
@@ -2111,10 +2077,10 @@
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A116" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B116" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C116" s="1">
         <v>129.98320871142414</v>
@@ -2122,10 +2088,10 @@
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A117" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B117" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C117" s="1">
         <v>154.41828732696882</v>
@@ -2133,10 +2099,10 @@
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A118" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B118" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C118" s="1">
         <v>107.93013211584199</v>
@@ -2144,10 +2110,10 @@
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A119" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B119" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C119" s="1">
         <v>187.3759</v>
@@ -2155,10 +2121,10 @@
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A120" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B120" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C120" s="1">
         <v>104.93934061698035</v>
@@ -2166,10 +2132,10 @@
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A121" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B121" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C121" s="1">
         <v>110.00000000000001</v>
@@ -2177,10 +2143,10 @@
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A122" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B122" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C122" s="1">
         <v>82.886830000000003</v>
@@ -2188,10 +2154,10 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A123" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B123" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C123" s="1">
         <v>135.30741531307629</v>
@@ -2199,10 +2165,10 @@
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A124" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B124" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C124" s="1">
         <v>161.11888111888112</v>
@@ -2210,10 +2176,10 @@
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A125" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B125" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C125" s="1">
         <v>165.76976421636616</v>
@@ -2221,10 +2187,10 @@
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A126" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B126" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C126" s="1">
         <v>115.8587</v>
@@ -2232,10 +2198,10 @@
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A127" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B127" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C127" s="1">
         <v>107.15987953726221</v>
@@ -2243,10 +2209,10 @@
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A128" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B128" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C128" s="1">
         <v>123.8981</v>
@@ -2254,10 +2220,10 @@
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A129" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B129" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C129" s="1">
         <v>103.6219686563652</v>
@@ -2265,10 +2231,10 @@
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A130" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B130" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C130" s="1">
         <v>99.90052</v>
@@ -2276,10 +2242,10 @@
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A131" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B131" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C131" s="1">
         <v>102.92852185981958</v>
@@ -2287,10 +2253,10 @@
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A132" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B132" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C132" s="1">
         <v>148.40091167636444</v>
@@ -2298,10 +2264,10 @@
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A133" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B133" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C133" s="1">
         <v>130.30510000000001</v>
@@ -2309,10 +2275,10 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A134" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B134" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C134" s="1">
         <v>29.020152883947183</v>
@@ -2320,10 +2286,10 @@
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A135" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B135" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C135" s="1">
         <v>20.732446111990583</v>
@@ -2331,10 +2297,10 @@
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A136" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B136" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C136" s="1">
         <v>28.595905636097093</v>
@@ -2342,10 +2308,10 @@
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A137" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B137" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C137" s="1">
         <v>24.095447924296373</v>
@@ -2353,10 +2319,10 @@
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A138" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B138" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C138" s="1">
         <v>26.030902859860817</v>
@@ -2364,10 +2330,10 @@
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A139" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B139" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C139" s="1">
         <v>23.959772801974655</v>
@@ -2375,10 +2341,10 @@
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A140" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B140" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C140" s="1">
         <v>26.156199999999998</v>
@@ -2386,10 +2352,10 @@
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A141" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B141" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C141" s="1">
         <v>22.105101295604548</v>
@@ -2397,10 +2363,10 @@
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A142" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B142" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C142" s="1">
         <v>32.090466666666671</v>
@@ -2408,10 +2374,10 @@
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A143" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B143" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C143" s="1">
         <v>16.354266998800973</v>
@@ -2419,10 +2385,10 @@
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A144" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B144" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C144" s="1">
         <v>19.211990696384206</v>
@@ -2430,10 +2396,10 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A145" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B145" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C145" s="1">
         <v>27.566739999999999</v>
@@ -2441,10 +2407,10 @@
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A146" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B146" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C146" s="1">
         <v>27.742728221016407</v>
@@ -2452,10 +2418,10 @@
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A147" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B147" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C147" s="1">
         <v>24.928907504105393</v>
@@ -2463,10 +2429,10 @@
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A148" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B148" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C148" s="1">
         <v>13.27159646951012</v>
@@ -2474,10 +2440,10 @@
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A149" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B149" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C149" s="1">
         <v>15.851147895986966</v>
@@ -2485,10 +2451,10 @@
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A150" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B150" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C150" s="1">
         <v>17.276902280156335</v>
@@ -2496,10 +2462,10 @@
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A151" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B151" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C151" s="1">
         <v>23.030768700502957</v>
@@ -2507,10 +2473,10 @@
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A152" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B152" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C152" s="1">
         <v>14.179349999999999</v>
@@ -2518,10 +2484,10 @@
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A153" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B153" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C153" s="1">
         <v>28.202490621798834</v>
@@ -2529,10 +2495,10 @@
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A154" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B154" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C154" s="1">
         <v>24</v>
@@ -2540,10 +2506,10 @@
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A155" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B155" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C155" s="1">
         <v>20.440919999999998</v>
@@ -2551,10 +2517,10 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A156" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B156" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C156" s="1">
         <v>25.022829794997886</v>
@@ -2562,10 +2528,10 @@
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A157" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B157" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C157" s="1">
         <v>15.104895104895105</v>
@@ -2573,10 +2539,10 @@
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A158" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B158" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C158" s="1">
         <v>17.975034674063799</v>
@@ -2584,10 +2550,10 @@
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A159" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B159" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C159" s="1">
         <v>25.443760000000001</v>
@@ -2595,10 +2561,10 @@
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A160" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B160" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C160" s="1">
         <v>23.455743314803502</v>
@@ -2606,10 +2572,10 @@
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A161" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B161" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C161" s="1">
         <v>13.95561</v>
@@ -2617,10 +2583,10 @@
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A162" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B162" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C162" s="1">
         <v>29.412386202766559</v>
@@ -2628,10 +2594,10 @@
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A163" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B163" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C163" s="1">
         <v>22.013280000000002</v>
@@ -2639,10 +2605,10 @@
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A164" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B164" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C164" s="1">
         <v>19.986120749479529</v>
@@ -2650,10 +2616,10 @@
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A165" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B165" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C165" s="1">
         <v>11.568416441556378</v>
@@ -2661,10 +2627,10 @@
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A166" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B166" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C166" s="1">
         <v>9.4800880000000003</v>
@@ -2672,10 +2638,10 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A167" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B167" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C167" s="1">
         <v>57.539958304378032</v>
@@ -2683,10 +2649,10 @@
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A168" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B168" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C168" s="1">
         <v>31.53862367056886</v>
@@ -2694,10 +2660,10 @@
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A169" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B169" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C169" s="1">
         <v>30.013148132310945</v>
@@ -2705,10 +2671,10 @@
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A170" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B170" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C170" s="1">
         <v>51.699988948425712</v>
@@ -2716,10 +2682,10 @@
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A171" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B171" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C171" s="1">
         <v>44.893193373859368</v>
@@ -2727,10 +2693,10 @@
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A172" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B172" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C172" s="1">
         <v>40.128020308239904</v>
@@ -2738,10 +2704,10 @@
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A173" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B173" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C173" s="1">
         <v>80.916034999999994</v>
@@ -2749,10 +2715,10 @@
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A174" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B174" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C174" s="1">
         <v>17.323796015366931</v>
@@ -2760,10 +2726,10 @@
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A175" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B175" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C175" s="1">
         <v>52.598188333333333</v>
@@ -2771,10 +2737,10 @@
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A176" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B176" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C176" s="1">
         <v>26.090117649938428</v>
@@ -2782,10 +2748,10 @@
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A177" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B177" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C177" s="1">
         <v>35.984075787898718</v>
@@ -2793,10 +2759,10 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A178" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B178" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C178" s="1">
         <v>71.742231000000004</v>
@@ -2804,10 +2770,10 @@
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A179" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B179" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C179" s="1">
         <v>43.145596687386792</v>
@@ -2815,10 +2781,10 @@
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A180" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B180" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C180" s="1">
         <v>97.724182666937281</v>
@@ -2826,10 +2792,10 @@
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A181" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B181" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C181" s="1">
         <v>42.310000205228903</v>
@@ -2837,10 +2803,10 @@
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A182" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B182" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C182" s="1">
         <v>39.338377512827442</v>
@@ -2848,10 +2814,10 @@
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A183" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B183" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C183" s="1">
         <v>41.508647578297911</v>
@@ -2859,10 +2825,10 @@
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A184" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B184" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C184" s="1">
         <v>42.175576465722266</v>
@@ -2870,10 +2836,10 @@
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A185" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B185" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C185" s="1">
         <v>45.569689999999994</v>
@@ -2881,10 +2847,10 @@
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A186" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B186" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C186" s="1">
         <v>46.143169707071749</v>
@@ -2892,10 +2858,10 @@
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A187" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B187" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C187" s="1">
         <v>59</v>
@@ -2903,10 +2869,10 @@
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A188" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B188" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C188" s="1">
         <v>76.614153000000016</v>
@@ -2914,10 +2880,10 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A189" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B189" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C189" s="1">
         <v>38.509351473922443</v>
@@ -2925,10 +2891,10 @@
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A190" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B190" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C190" s="1">
         <v>35.244755244755247</v>
@@ -2936,10 +2902,10 @@
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A191" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B191" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C191" s="1">
         <v>31.955617198335645</v>
@@ -2947,10 +2913,10 @@
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A192" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B192" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C192" s="1">
         <v>53.7303815</v>
@@ -2958,10 +2924,10 @@
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A193" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B193" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C193" s="1">
         <v>33.347061416756468</v>
@@ -2969,10 +2935,10 @@
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A194" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B194" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C194" s="1">
         <v>59.827740000000006</v>
@@ -2980,10 +2946,10 @@
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A195" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B195" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C195" s="1">
         <v>62.452037288484021</v>
@@ -2991,10 +2957,10 @@
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A196" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B196" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C196" s="1">
         <v>65.190475000000006</v>
@@ -3002,10 +2968,10 @@
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A197" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B197" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C197" s="1">
         <v>32.977099236641223</v>
@@ -3013,10 +2979,10 @@
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A198" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B198" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C198" s="1">
         <v>22.114080799934882</v>
@@ -3024,10 +2990,10 @@
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A199" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B199" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C199" s="1">
         <v>40.909678700000001</v>
@@ -3035,10 +3001,10 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A200" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B200" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C200" s="1">
         <v>512.35580264072269</v>
@@ -3046,10 +3012,10 @@
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A201" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B201" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C201" s="1">
         <v>498.29162266732834</v>
@@ -3057,10 +3023,10 @@
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A202" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B202" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C202" s="1">
         <v>512.86023944507031</v>
@@ -3068,10 +3034,10 @@
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A203" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B203" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C203" s="1">
         <v>520</v>
@@ -3079,10 +3045,10 @@
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A204" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B204" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C204" s="1">
         <v>488.60752360280503</v>
@@ -3090,10 +3056,10 @@
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A205" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B205" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C205" s="1">
         <v>530.01527932441195</v>
@@ -3101,10 +3067,10 @@
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A206" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B206" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C206" s="1">
         <v>508.2611</v>
@@ -3112,10 +3078,10 @@
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A207" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B207" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C207" s="1">
         <v>512.97463006601299</v>
@@ -3123,10 +3089,10 @@
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A208" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B208" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C208" s="1">
         <v>498.38150000000002</v>
@@ -3134,10 +3100,10 @@
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A209" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B209" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C209" s="1">
         <v>500.03293481623052</v>
@@ -3145,10 +3111,10 @@
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A210" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B210" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C210" s="1">
         <v>505.89669795063986</v>
@@ -3156,10 +3122,10 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A211" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B211" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C211" s="1">
         <v>491.25420000000003</v>
@@ -3167,10 +3133,10 @@
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A212" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B212" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C212" s="1">
         <v>513.32088598242979</v>
@@ -3178,10 +3144,10 @@
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A213" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B213" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C213" s="1">
         <v>442.02093750576597</v>
@@ -3189,10 +3155,10 @@
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A214" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B214" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C214" s="1">
         <v>471.35074889140753</v>
@@ -3200,10 +3166,10 @@
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A215" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B215" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C215" s="1">
         <v>512.28976055896999</v>
@@ -3211,10 +3177,10 @@
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A216" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B216" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C216" s="1">
         <v>503.06893841806334</v>
@@ -3222,10 +3188,10 @@
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A217" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B217" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C217" s="1">
         <v>518.17335730136892</v>
@@ -3233,10 +3199,10 @@
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A218" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B218" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C218" s="1">
         <v>498.69540000000001</v>
@@ -3244,10 +3210,10 @@
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A219" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B219" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C219" s="1">
         <v>502.77631874819303</v>
@@ -3255,10 +3221,10 @@
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A220" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B220" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C220" s="1">
         <v>526</v>
@@ -3266,10 +3232,10 @@
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A221" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B221" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C221" s="1">
         <v>492.12389999999999</v>
@@ -3277,10 +3243,10 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A222" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B222" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C222" s="1">
         <v>508.94066489793613</v>
@@ -3288,10 +3254,10 @@
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A223" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B223" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C223" s="1">
         <v>505.51048951048955</v>
@@ -3299,10 +3265,10 @@
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A224" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B224" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C224" s="1">
         <v>501.30374479889042</v>
@@ -3310,10 +3276,10 @@
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A225" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B225" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C225" s="1">
         <v>515.66189999999995</v>
@@ -3321,10 +3287,10 @@
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A226" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B226" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C226" s="1">
         <v>482.70098676994348</v>
@@ -3332,10 +3298,10 @@
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A227" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B227" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C227" s="1">
         <v>514.58169999999996</v>
@@ -3343,10 +3309,10 @@
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A228" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B228" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C228" s="1">
         <v>508.11057904086522</v>
@@ -3354,10 +3320,10 @@
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A229" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B229" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C229" s="1">
         <v>528.01949999999999</v>
@@ -3365,10 +3331,10 @@
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A230" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B230" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C230" s="1">
         <v>541.62387231089519</v>
@@ -3376,10 +3342,10 @@
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A231" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B231" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C231" s="1">
         <v>528.14137472816958</v>
@@ -3387,10 +3353,10 @@
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A232" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B232" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C232" s="1">
         <v>553.14170000000001</v>
@@ -3398,10 +3364,10 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A233" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B233" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C233" s="1">
         <v>89.06184850590688</v>
@@ -3409,10 +3375,10 @@
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A234" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B234" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C234" s="1">
         <v>78.83640556233911</v>
@@ -3420,10 +3386,10 @@
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A235" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B235" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C235" s="1">
         <v>98.516408364348706</v>
@@ -3431,10 +3397,10 @@
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A236" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B236" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C236" s="1">
         <v>64.819712591585883</v>
@@ -3442,10 +3408,10 @@
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A237" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B237" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C237" s="1">
         <v>119.15340996707874</v>
@@ -3453,10 +3419,10 @@
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A238" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B238" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C238" s="1">
         <v>78.996206958996609</v>
@@ -3464,10 +3430,10 @@
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A239" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B239" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C239" s="1">
         <v>80.645830000000004</v>
@@ -3475,10 +3441,10 @@
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A240" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B240" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C240" s="1">
         <v>132.75710778104158</v>
@@ -3486,10 +3452,10 @@
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A241" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B241" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C241" s="1">
         <v>94.963149999999999</v>
@@ -3497,10 +3463,10 @@
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A242" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B242" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C242" s="1">
         <v>127.53410855795852</v>
@@ -3508,10 +3474,10 @@
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A243" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B243" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C243" s="1">
         <v>101.12999975600407</v>
@@ -3519,10 +3485,10 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A244" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B244" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C244" s="1">
         <v>75.386560000000003</v>
@@ -3530,10 +3496,10 @@
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A245" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B245" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C245" s="1">
         <v>126.97485465501927</v>
@@ -3541,10 +3507,10 @@
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A246" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B246" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C246" s="1">
         <v>93.454217945642753</v>
@@ -3552,10 +3518,10 @@
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A247" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B247" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C247" s="1">
         <v>116.9425415210389</v>
@@ -3563,10 +3529,10 @@
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A248" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B248" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C248" s="1">
         <v>88.867320953693778</v>
@@ -3574,10 +3540,10 @@
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A249" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B249" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C249" s="1">
         <v>88.205404975788554</v>
@@ -3585,10 +3551,10 @@
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A250" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B250" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C250" s="1">
         <v>112.22232739169974</v>
@@ -3596,10 +3562,10 @@
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A251" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B251" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C251" s="1">
         <v>77.002549999999999</v>
@@ -3607,10 +3573,10 @@
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A252" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B252" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C252" s="1">
         <v>114.30819035517595</v>
@@ -3618,10 +3584,10 @@
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A253" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B253" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C253" s="1">
         <v>80</v>
@@ -3629,10 +3595,10 @@
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A254" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B254" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C254" s="1">
         <v>79.379769999999994</v>
@@ -3640,10 +3606,10 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A255" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B255" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C255" s="1">
         <v>90.718431379645509</v>
@@ -3651,10 +3617,10 @@
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A256" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B256" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C256" s="1">
         <v>111.77622377622379</v>
@@ -3662,10 +3628,10 @@
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A257" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B257" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C257" s="1">
         <v>85.88072122052705</v>
@@ -3673,10 +3639,10 @@
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A258" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B258" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C258" s="1">
         <v>125.5582</v>
@@ -3684,10 +3650,10 @@
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A259" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B259" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C259" s="1">
         <v>82.535617620690005</v>
@@ -3695,10 +3661,10 @@
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A260" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B260" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C260" s="1">
         <v>117.5817</v>
@@ -3706,10 +3672,10 @@
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A261" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B261" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C261" s="1">
         <v>79.252173945979465</v>
@@ -3717,10 +3683,10 @@
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A262" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B262" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C262" s="1">
         <v>62.747669999999999</v>
@@ -3728,10 +3694,10 @@
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A263" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B263" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C263" s="1">
         <v>99.93060374739764</v>
@@ -3739,10 +3705,10 @@
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A264" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B264" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C264" s="1">
         <v>83.855191600655957</v>
@@ -3750,10 +3716,10 @@
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A265" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B265" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C265" s="1">
         <v>72.385310000000004</v>
@@ -3761,10 +3727,10 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A266" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B266" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C266" s="1">
         <v>56.038915913829051</v>
@@ -3772,10 +3738,10 @@
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A267" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B267" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C267" s="1">
         <v>54.956889898288104</v>
@@ -3783,10 +3749,10 @@
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A268" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B268" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C268" s="1">
         <v>52.669703040436566</v>
@@ -3794,10 +3760,10 @@
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A269" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B269" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C269" s="1">
         <v>52.03722931810475</v>
@@ -3805,10 +3771,10 @@
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A270" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B270" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C270" s="1">
         <v>51.598361393514267</v>
@@ -3816,10 +3782,10 @@
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A271" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B271" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C271" s="1">
         <v>53.661658610388415</v>
@@ -3827,10 +3793,10 @@
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A272" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B272" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C272" s="1">
         <v>51.58296</v>
@@ -3838,10 +3804,10 @@
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A273" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B273" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C273" s="1">
         <v>106.51480624295114</v>
@@ -3849,10 +3815,10 @@
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A274" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B274" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C274" s="1">
         <v>54.677883333333327</v>
@@ -3860,10 +3826,10 @@
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A275" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B275" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C275" s="1">
         <v>57.036512094082539</v>
@@ -3871,10 +3837,10 @@
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A276" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B276" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C276" s="1">
         <v>76.112454503358023</v>
@@ -3882,10 +3848,10 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A277" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B277" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C277" s="1">
         <v>42.272910000000003</v>
@@ -3893,10 +3859,10 @@
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A278" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B278" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C278" s="1">
         <v>67.512477365072243</v>
@@ -3904,10 +3870,10 @@
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A279" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B279" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C279" s="1">
         <v>84.562960864992505</v>
@@ -3915,10 +3881,10 @@
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A280" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B280" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C280" s="1">
         <v>89.554130663151426</v>
@@ -3926,10 +3892,10 @@
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A281" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B281" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C281" s="1">
         <v>40.139126199077957</v>
@@ -3937,10 +3903,10 @@
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A282" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B282" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C282" s="1">
         <v>54.26430611976361</v>
@@ -3948,10 +3914,10 @@
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A283" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B283" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C283" s="1">
         <v>55.272546259104004</v>
@@ -3959,10 +3925,10 @@
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A284" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B284" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C284" s="1">
         <v>57.885890000000003</v>
@@ -3970,10 +3936,10 @@
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A285" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B285" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C285" s="1">
         <v>64.506110910836597</v>
@@ -3981,10 +3947,10 @@
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A286" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B286" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C286" s="1">
         <v>42</v>
@@ -3992,10 +3958,10 @@
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A287" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B287" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C287" s="1">
         <v>55.769260000000003</v>
@@ -4003,10 +3969,10 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A288" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B288" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C288" s="1">
         <v>57.459727876061407</v>
@@ -4014,10 +3980,10 @@
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A289" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B289" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C289" s="1">
         <v>58.405594405594407</v>
@@ -4025,10 +3991,10 @@
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A290" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B290" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C290" s="1">
         <v>40.943134535367548</v>
@@ -4036,10 +4002,10 @@
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A291" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B291" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C291" s="1">
         <v>50.572290000000002</v>
@@ -4047,10 +4013,10 @@
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A292" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B292" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C292" s="1">
         <v>57.232921029731273</v>
@@ -4058,10 +4024,10 @@
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A293" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B293" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C293" s="1">
         <v>49.633290000000002</v>
@@ -4069,10 +4035,10 @@
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A294" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B294" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C294" s="1">
         <v>57.841621355925632</v>
@@ -4080,10 +4046,10 @@
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A295" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B295" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C295" s="1">
         <v>57.438510000000001</v>
@@ -4091,10 +4057,10 @@
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A296" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B296" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C296" s="1">
         <v>51.963913948646777</v>
@@ -4102,10 +4068,10 @@
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A297" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B297" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C297" s="1">
         <v>75.493348438223663</v>
@@ -4113,10 +4079,10 @@
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A298" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B298" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C298" s="1">
         <v>69.551829999999995</v>
@@ -4124,10 +4090,10 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A299" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B299" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C299" s="1">
         <v>19.013203613620568</v>
@@ -4135,10 +4101,10 @@
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A300" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B300" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C300" s="1">
         <v>32.078530000000001</v>
@@ -4146,10 +4112,10 @@
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A301" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B301" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C301" s="1">
         <v>21.016577453322085</v>
@@ -4157,10 +4123,10 @@
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A302" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B302" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C302" s="1">
         <v>20.998791182177293</v>
@@ -4168,10 +4134,10 @@
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A303" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B303" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C303" s="1">
         <v>22.115072429813779</v>
@@ -4179,10 +4145,10 @@
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A304" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B304" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C304" s="1">
         <v>27.474674349967735</v>
@@ -4190,10 +4156,10 @@
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A305" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B305" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C305" s="1">
         <v>37.230849999999997</v>
@@ -4201,10 +4167,10 @@
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A306" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B306" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C306" s="1">
         <v>11.9611007010534</v>
@@ -4212,10 +4178,10 @@
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A307" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B307" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C307" s="1">
         <v>26.43525</v>
@@ -4223,10 +4189,10 @@
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A308" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B308" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C308" s="1">
         <v>27.687647892343549</v>
@@ -4234,10 +4200,10 @@
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A309" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B309" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C309" s="1">
         <v>12.931679252410685</v>
@@ -4245,10 +4211,10 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A310" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B310" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C310" s="1">
         <v>20.02075</v>
@@ -4256,10 +4222,10 @@
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A311" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B311" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C311" s="1">
         <v>38.214085977502052</v>
@@ -4267,10 +4233,10 @@
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A312" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B312" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C312" s="1">
         <v>10.222599959407347</v>
@@ -4278,10 +4244,10 @@
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A313" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B313" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C313" s="1">
         <v>27.188580130647171</v>
@@ -4289,10 +4255,10 @@
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A314" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B314" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C314" s="1">
         <v>24.990631279523889</v>
@@ -4300,10 +4266,10 @@
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A315" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B315" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C315" s="1">
         <v>15.962224001095137</v>
@@ -4311,10 +4277,10 @@
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A316" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B316" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C316" s="1">
         <v>33.237082050751781</v>
@@ -4322,10 +4288,10 @@
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A317" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B317" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C317" s="1">
         <v>13.57335</v>
@@ -4333,10 +4299,10 @@
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A318" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B318" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C318" s="1">
         <v>22.399997144600977</v>
@@ -4344,10 +4310,10 @@
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A319" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B319" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C319" s="1">
         <v>17</v>
@@ -4355,10 +4321,10 @@
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A320" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B320" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C320" s="1">
         <v>20.90907</v>
@@ -4366,10 +4332,10 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A321" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B321" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C321" s="1">
         <v>23.244835450771792</v>
@@ -4377,10 +4343,10 @@
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A322" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B322" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C322" s="1">
         <v>12.083916083916083</v>
@@ -4388,10 +4354,10 @@
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A323" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B323" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C323" s="1">
         <v>31.955617198335645</v>
@@ -4399,10 +4365,10 @@
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A324" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B324" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C324" s="1">
         <v>41.877960000000002</v>
@@ -4410,10 +4376,10 @@
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A325" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B325" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C325" s="1">
         <v>34.343945080217395</v>
@@ -4421,10 +4387,10 @@
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A326" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B326" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C326" s="1">
         <v>9.4654690000000006</v>
@@ -4432,10 +4398,10 @@
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A327" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B327" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C327" s="1">
         <v>19.362315398020446</v>
@@ -4443,10 +4409,10 @@
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A328" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B328" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C328" s="1">
         <v>17.946539999999999</v>
@@ -4454,10 +4420,10 @@
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A329" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B329" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C329" s="1">
         <v>22.984038861901457</v>
@@ -4465,10 +4431,10 @@
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A330" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B330" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C330" s="1">
         <v>5.4987046680172682</v>
@@ -4476,10 +4442,10 @@
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A331" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B331" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C331" s="1">
         <v>5.085051</v>
@@ -4487,10 +4453,10 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A332" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B332" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C332" s="1">
         <v>6.004169562195969</v>
@@ -4498,10 +4464,10 @@
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A333" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B333" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C333" s="1">
         <v>9.4315519999999999</v>
@@ -4509,10 +4475,10 @@
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A334" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B334" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C334" s="1">
         <v>15.365885508381385</v>
@@ -4520,10 +4486,10 @@
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A335" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B335" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C335" s="1">
         <v>5.6058645351740521</v>
@@ -4531,10 +4497,10 @@
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A336" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B336" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C336" s="1">
         <v>7.4393849701311812</v>
@@ -4542,10 +4508,10 @@
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A337" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B337" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C337" s="1">
         <v>7.861109817244885</v>
@@ -4553,10 +4519,10 @@
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A338" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B338" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C338" s="1">
         <v>7.7142920000000004</v>
@@ -4564,10 +4530,10 @@
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A339" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B339" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C339" s="1">
         <v>14.842220869919055</v>
@@ -4575,10 +4541,10 @@
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A340" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B340" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C340" s="1">
         <v>13.528251666666668</v>
@@ -4586,10 +4552,10 @@
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A341" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B341" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C341" s="1">
         <v>5.0861775222942098</v>
@@ -4597,10 +4563,10 @@
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A342" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B342" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C342" s="1">
         <v>5.6407005961715173</v>
@@ -4608,10 +4574,10 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A343" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B343" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C343" s="1">
         <v>41.727780000000003</v>
@@ -4619,10 +4585,10 @@
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A344" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B344" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C344" s="1">
         <v>5.8233125546677647</v>
@@ -4630,10 +4596,10 @@
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A345" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B345" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C345" s="1">
         <v>4.4493138434970723</v>
@@ -4641,10 +4607,10 @@
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A346" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B346" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C346" s="1">
         <v>4.7963008260519171</v>
@@ -4652,10 +4618,10 @@
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A347" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B347" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C347" s="1">
         <v>1.346944277184978</v>
@@ -4663,10 +4629,10 @@
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A348" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B348" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C348" s="1">
         <v>12.44199549803934</v>
@@ -4674,10 +4640,10 @@
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A349" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B349" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C349" s="1">
         <v>7.2061970000000004</v>
@@ -4685,10 +4651,10 @@
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A350" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B350" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C350" s="1">
         <v>6.6449189958989336</v>
@@ -4696,10 +4662,10 @@
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A351" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B351" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C351" s="1">
         <v>6</v>
@@ -4707,10 +4673,10 @@
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A352" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B352" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C352" s="1">
         <v>8.0566270000000006</v>
@@ -4718,10 +4684,10 @@
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A353" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B353" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C353" s="1">
         <v>2.8145949599315601</v>
@@ -4729,10 +4695,10 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A354" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B354" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C354" s="1">
         <v>10.573426573426573</v>
@@ -4740,10 +4706,10 @@
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A355" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B355" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C355" s="1">
         <v>4.993065187239945</v>
@@ -4751,10 +4717,10 @@
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A356" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B356" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C356" s="1">
         <v>9.2118359999999999</v>
@@ -4762,10 +4728,10 @@
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A357" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B357" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C357" s="1">
         <v>8.8201251062107993</v>
@@ -4773,10 +4739,10 @@
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A358" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B358" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C358" s="1">
         <v>2.5805099999999999</v>
@@ -4784,10 +4750,10 @@
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A359" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B359" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C359" s="1">
         <v>7.013407728764264</v>
@@ -4795,10 +4761,10 @@
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A360" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B360" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C360" s="1">
         <v>8.2255129999999994</v>
@@ -4806,10 +4772,10 @@
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A361" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B361" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C361" s="1">
         <v>1.9986120749479528</v>
@@ -4817,10 +4783,10 @@
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A362" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B362" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C362" s="1">
         <v>4.6092055871927444</v>
@@ -4828,10 +4794,10 @@
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A363" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B363" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C363" s="1">
         <v>5.1077050000000002</v>
@@ -4839,10 +4805,10 @@
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A364" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B364" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C364" s="1">
         <v>40.006949270326601</v>
@@ -4850,10 +4816,10 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A365" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B365" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C365" s="1">
         <v>81.770629999999997</v>
@@ -4861,10 +4827,10 @@
     </row>
     <row r="366" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A366" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B366" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C366" s="1">
         <v>50.476242090157889</v>
@@ -4872,10 +4838,10 @@
     </row>
     <row r="367" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A367" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B367" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C367" s="1">
         <v>53.476652016212057</v>
@@ -4883,10 +4849,10 @@
     </row>
     <row r="368" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A368" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B368" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C368" s="1">
         <v>81.371521458505086</v>
@@ -4894,10 +4860,10 @@
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A369" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B369" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C369" s="1">
         <v>37.624863200050292</v>
@@ -4905,10 +4871,10 @@
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A370" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B370" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C370" s="1">
         <v>54.645980000000002</v>
@@ -4916,10 +4882,10 @@
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A371" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B371" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C371" s="1">
         <v>55.20107323539623</v>
@@ -4927,10 +4893,10 @@
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A372" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B372" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C372" s="1">
         <v>60.646949999999997</v>
@@ -4938,10 +4904,10 @@
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A373" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B373" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C373" s="1">
         <v>56.327788336975217</v>
@@ -4949,10 +4915,10 @@
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A374" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B374" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C374" s="1">
         <v>35.133410175558687</v>
@@ -4960,10 +4926,10 @@
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A375" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B375" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C375" s="1">
         <v>48.954450000000001</v>
@@ -4971,10 +4937,10 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A376" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B376" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C376" s="1">
         <v>65.35720679671374</v>
@@ -4982,10 +4948,10 @@
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A377" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B377" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C377" s="1">
         <v>16.912066166023951</v>
@@ -4993,10 +4959,10 @@
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A378" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B378" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C378" s="1">
         <v>42.215919827237563</v>
@@ -5004,10 +4970,10 @@
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A379" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B379" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C379" s="1">
         <v>35.084831672702961</v>
@@ -5015,10 +4981,10 @@
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A380" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B380" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C380" s="1">
         <v>31.78246079106755</v>
@@ -5026,10 +4992,10 @@
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A381" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B381" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C381" s="1">
         <v>32.301265480461019</v>
@@ -5037,10 +5003,10 @@
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A382" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B382" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C382" s="1">
         <v>44.155830000000002</v>
@@ -5048,10 +5014,10 @@
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A383" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B383" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C383" s="1">
         <v>72.561856865985433</v>
@@ -5059,10 +5025,10 @@
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A384" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B384" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C384" s="1">
         <v>69</v>
@@ -5070,10 +5036,10 @@
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A385" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B385" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C385" s="1">
         <v>57.0152</v>
@@ -5081,10 +5047,10 @@
     </row>
     <row r="386" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A386" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B386" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C386" s="1">
         <v>45.137010330567357</v>
@@ -5092,10 +5058,10 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A387" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B387" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C387" s="1">
         <v>43.804195804195807</v>
@@ -5103,10 +5069,10 @@
     </row>
     <row r="388" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A388" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B388" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C388" s="1">
         <v>61.914008321775313</v>
@@ -5114,10 +5080,10 @@
     </row>
     <row r="389" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A389" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B389" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C389" s="1">
         <v>50.793500000000002</v>
@@ -5125,10 +5091,10 @@
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A390" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B390" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C390" s="1">
         <v>52.703188099824906</v>
@@ -5136,10 +5102,10 @@
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A391" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B391" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C391" s="1">
         <v>68.120159999999998</v>
@@ -5147,10 +5113,10 @@
     </row>
     <row r="392" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A392" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B392" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C392" s="1">
         <v>47.42831765130417</v>
@@ -5158,10 +5124,10 @@
     </row>
     <row r="393" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A393" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B393" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C393" s="1">
         <v>43.543680000000002</v>
@@ -5169,10 +5135,10 @@
     </row>
     <row r="394" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A394" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B394" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C394" s="1">
         <v>22.984038861901457</v>
@@ -5180,10 +5146,10 @@
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A395" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B395" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C395" s="1">
         <v>73.257531310254521</v>
@@ -5191,10 +5157,10 @@
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A396" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B396" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C396" s="1">
         <v>82.146140000000003</v>
@@ -5202,10 +5168,10 @@
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A397" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B397" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C397" s="1">
         <v>140.09728978457267</v>
@@ -5213,10 +5179,10 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A398" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B398" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C398" s="1">
         <v>108.82629667475206</v>
@@ -5224,10 +5190,10 @@
     </row>
     <row r="399" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A399" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B399" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C399" s="1">
         <v>130.56785599087419</v>
@@ -5235,10 +5201,10 @@
     </row>
     <row r="400" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A400" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B400" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C400" s="1">
         <v>109.37061833330586</v>
@@ -5246,10 +5212,10 @@
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A401" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B401" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C401" s="1">
         <v>122.97380825958031</v>
@@ -5257,10 +5223,10 @@
     </row>
     <row r="402" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A402" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B402" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C402" s="1">
         <v>122.16253682495501</v>
@@ -5268,10 +5234,10 @@
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A403" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B403" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C403" s="1">
         <v>118.1499</v>
@@ -5279,10 +5245,10 @@
     </row>
     <row r="404" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A404" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B404" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C404" s="1">
         <v>113.84890667281091</v>
@@ -5290,10 +5256,10 @@
     </row>
     <row r="405" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A405" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B405" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C405" s="1">
         <v>118.46509999999999</v>
@@ -5301,10 +5267,10 @@
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A406" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B406" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C406" s="1">
         <v>136.96944778092217</v>
@@ -5312,10 +5278,10 @@
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A407" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B407" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C407" s="1">
         <v>133.89768678936619</v>
@@ -5323,10 +5289,10 @@
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A408" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B408" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C408" s="1">
         <v>85.135099999999994</v>
@@ -5334,10 +5300,10 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A409" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B409" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C409" s="1">
         <v>103.69272210894766</v>
@@ -5345,10 +5311,10 @@
     </row>
     <row r="410" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A410" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B410" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C410" s="1">
         <v>103.22465726885251</v>
@@ -5356,10 +5322,10 @@
     </row>
     <row r="411" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A411" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B411" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C411" s="1">
         <v>102.00117609047734</v>
@@ -5367,10 +5333,10 @@
     </row>
     <row r="412" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A412" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B412" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C412" s="1">
         <v>123.29731679890583</v>
@@ -5378,10 +5344,10 @@
     </row>
     <row r="413" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A413" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B413" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C413" s="1">
         <v>136.78433735237309</v>
@@ -5389,10 +5355,10 @@
     </row>
     <row r="414" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A414" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B414" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C414" s="1">
         <v>116.07331991759663</v>
@@ -5400,10 +5366,10 @@
     </row>
     <row r="415" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A415" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B415" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C415" s="1">
         <v>65.659930000000003</v>
@@ -5411,10 +5377,10 @@
     </row>
     <row r="416" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A416" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B416" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C416" s="1">
         <v>112.52282356132505</v>
@@ -5422,10 +5388,10 @@
     </row>
     <row r="417" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A417" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B417" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C417" s="1">
         <v>124</v>
@@ -5433,10 +5399,10 @@
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A418" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B418" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C418" s="1">
         <v>128.6927</v>
@@ -5444,10 +5410,10 @@
     </row>
     <row r="419" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A419" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B419" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C419" s="1">
         <v>121.83656389840486</v>
@@ -5455,10 +5421,10 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A420" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B420" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C420" s="1">
         <v>113.79020979020979</v>
@@ -5466,10 +5432,10 @@
     </row>
     <row r="421" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A421" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B421" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C421" s="1">
         <v>119.83356449375867</v>
@@ -5477,10 +5443,10 @@
     </row>
     <row r="422" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A422" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B422" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C422" s="1">
         <v>129.44040000000001</v>
@@ -5488,10 +5454,10 @@
     </row>
     <row r="423" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A423" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B423" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C423" s="1">
         <v>113.294143192852</v>
@@ -5499,10 +5465,10 @@
     </row>
     <row r="424" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A424" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B424" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C424" s="1">
         <v>124.0316</v>
@@ -5510,10 +5476,10 @@
     </row>
     <row r="425" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A425" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B425" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C425" s="1">
         <v>133.31918590437161</v>
@@ -5521,10 +5487,10 @@
     </row>
     <row r="426" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A426" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B426" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C426" s="1">
         <v>148.30840000000001</v>
@@ -5532,10 +5498,10 @@
     </row>
     <row r="427" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A427" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B427" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C427" s="1">
         <v>126.91186675919501</v>
@@ -5543,10 +5509,10 @@
     </row>
     <row r="428" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A428" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B428" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C428" s="1">
         <v>61.43724169710584</v>
@@ -5554,10 +5520,10 @@
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A429" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B429" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C429" s="1">
         <v>131.7347</v>
@@ -5565,10 +5531,10 @@
     </row>
     <row r="430" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A430" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B430" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C430" s="1">
         <v>76.073662265462005</v>
@@ -5576,10 +5542,10 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A431" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B431" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C431" s="1">
         <v>59.1023</v>
@@ -5587,10 +5553,10 @@
     </row>
     <row r="432" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A432" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B432" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C432" s="1">
         <v>121.92358269299274</v>
@@ -5598,10 +5564,10 @@
     </row>
     <row r="433" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A433" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B433" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C433" s="1">
         <v>89.481520225318235</v>
@@ -5609,10 +5575,10 @@
     </row>
     <row r="434" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A434" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B434" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C434" s="1">
         <v>94.945025968846736</v>
@@ -5620,10 +5586,10 @@
     </row>
     <row r="435" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A435" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B435" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C435" s="1">
         <v>114.283895452449</v>
@@ -5631,10 +5597,10 @@
     </row>
     <row r="436" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A436" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B436" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C436" s="1">
         <v>113.24769999999999</v>
@@ -5642,10 +5608,10 @@
     </row>
     <row r="437" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A437" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B437" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C437" s="1">
         <v>97.689345725681093</v>
@@ -5653,10 +5619,10 @@
     </row>
     <row r="438" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A438" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B438" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C438" s="1">
         <v>112.07628333333334</v>
@@ -5664,10 +5630,10 @@
     </row>
     <row r="439" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A439" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B439" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C439" s="1">
         <v>115.32013676176663</v>
@@ -5675,10 +5641,10 @@
     </row>
     <row r="440" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A440" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B440" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C440" s="1">
         <v>93.746224509750945</v>
@@ -5686,10 +5652,10 @@
     </row>
     <row r="441" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A441" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B441" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C441" s="1">
         <v>116.4735</v>
@@ -5697,10 +5663,10 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A442" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B442" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C442" s="1">
         <v>110.17128950106543</v>
@@ -5708,10 +5674,10 @@
     </row>
     <row r="443" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A443" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B443" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C443" s="1">
         <v>147.95324925733897</v>
@@ -5719,10 +5685,10 @@
     </row>
     <row r="444" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A444" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B444" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C444" s="1">
         <v>82.405213949190042</v>
@@ -5730,10 +5696,10 @@
     </row>
     <row r="445" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A445" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B445" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C445" s="1">
         <v>80.672233538197347</v>
@@ -5741,10 +5707,10 @@
     </row>
     <row r="446" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A446" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B446" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C446" s="1">
         <v>60.730836585721889</v>
@@ -5752,10 +5718,10 @@
     </row>
     <row r="447" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A447" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B447" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C447" s="1">
         <v>82.33203683229533</v>
@@ -5763,10 +5729,10 @@
     </row>
     <row r="448" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A448" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B448" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C448" s="1">
         <v>41.332120000000003</v>
@@ -5774,10 +5740,10 @@
     </row>
     <row r="449" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A449" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B449" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C449" s="1">
         <v>100.63439827819438</v>
@@ -5785,10 +5751,10 @@
     </row>
     <row r="450" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A450" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B450" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C450" s="1">
         <v>85</v>
@@ -5796,10 +5762,10 @@
     </row>
     <row r="451" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A451" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B451" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C451" s="1">
         <v>153.56970000000001</v>
@@ -5807,10 +5773,10 @@
     </row>
     <row r="452" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A452" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B452" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C452" s="1">
         <v>93.121383290499125</v>
@@ -5818,10 +5784,10 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A453" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B453" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C453" s="1">
         <v>60.419580419580399</v>
@@ -5829,10 +5795,10 @@
     </row>
     <row r="454" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A454" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B454" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C454" s="1">
         <v>91.872399445214981</v>
@@ -5840,10 +5806,10 @@
     </row>
     <row r="455" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A455" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B455" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C455" s="1">
         <v>84.725570000000005</v>
@@ -5851,10 +5817,10 @@
     </row>
     <row r="456" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A456" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B456" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C456" s="1">
         <v>112.323171034108</v>
@@ -5862,10 +5828,10 @@
     </row>
     <row r="457" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A457" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B457" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C457" s="1">
         <v>81.532989999999998</v>
@@ -5873,10 +5839,10 @@
     </row>
     <row r="458" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A458" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B458" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C458" s="1">
         <v>98.407709832329331</v>
@@ -5884,10 +5850,10 @@
     </row>
     <row r="459" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A459" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B459" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C459" s="1">
         <v>73.490920000000003</v>
@@ -5895,10 +5861,10 @@
     </row>
     <row r="460" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A460" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B460" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C460" s="1">
         <v>52.963219986120748</v>
@@ -5906,10 +5872,10 @@
     </row>
     <row r="461" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A461" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B461" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C461" s="1">
         <v>109.19343947153037</v>
@@ -5917,10 +5883,10 @@
     </row>
     <row r="462" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A462" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B462" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C462" s="1">
         <v>81.824600000000004</v>
